--- a/FCT.xlsx
+++ b/FCT.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/cc257be1a5798d86/WILLIAN/FCT Terça/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="113" documentId="13_ncr:1_{4721CD4C-DC5B-4D56-86E7-BD97B97F13DF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{CC48CCDD-0C3D-43D1-B04D-91BD69056E6A}"/>
+  <xr:revisionPtr revIDLastSave="212" documentId="13_ncr:1_{4721CD4C-DC5B-4D56-86E7-BD97B97F13DF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{8F1CCDF9-D84F-44C7-BFB8-DC747D9D1464}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{4C5D2070-0CD2-4A2B-85DD-4C1228673220}"/>
   </bookViews>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="130" uniqueCount="36">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="181" uniqueCount="40">
   <si>
     <t>Azul</t>
   </si>
@@ -147,6 +147,18 @@
   </si>
   <si>
     <t>Edu</t>
+  </si>
+  <si>
+    <t>Renan</t>
+  </si>
+  <si>
+    <t>Djow</t>
+  </si>
+  <si>
+    <t>Junior</t>
+  </si>
+  <si>
+    <t>Volber</t>
   </si>
 </sst>
 </file>
@@ -279,7 +291,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="16">
+  <cellXfs count="12">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -308,23 +320,11 @@
     <xf numFmtId="0" fontId="0" fillId="4" borderId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="3" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
+      <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -690,7 +690,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8E481E65-1F7A-4C5C-8819-A9B2DFE6B944}">
-  <dimension ref="A1:X13"/>
+  <dimension ref="A1:AH13"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="2" width="9.140625" style="1"/>
@@ -710,10 +710,19 @@
     <col min="18" max="18" width="12.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="19" max="22" width="9.140625" style="1"/>
     <col min="23" max="23" width="11.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="24" max="16384" width="9.140625" style="1"/>
+    <col min="24" max="25" width="9.140625" style="1"/>
+    <col min="26" max="26" width="9.140625" style="1" bestFit="1" customWidth="1"/>
+    <col min="27" max="27" width="8.28515625" style="1" bestFit="1" customWidth="1"/>
+    <col min="28" max="28" width="12.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="29" max="29" width="7.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="30" max="30" width="9.140625" style="1"/>
+    <col min="31" max="31" width="11.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="32" max="32" width="9.140625" style="1"/>
+    <col min="33" max="33" width="11.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="34" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:24" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:34" x14ac:dyDescent="0.25">
       <c r="A1" s="2"/>
       <c r="B1" s="2" t="s">
         <v>20</v>
@@ -754,570 +763,800 @@
         <v>46266</v>
       </c>
       <c r="X1" s="2"/>
+      <c r="Z1" s="2"/>
+      <c r="AA1" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="AB1" s="2">
+        <v>46273</v>
+      </c>
+      <c r="AC1" s="2"/>
+      <c r="AE1" s="2"/>
+      <c r="AF1" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="AG1" s="2">
+        <v>46280</v>
+      </c>
+      <c r="AH1" s="2"/>
     </row>
-    <row r="2" spans="1:24" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A2" s="14" t="s">
+    <row r="2" spans="1:34" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A2" s="5" t="s">
         <v>0</v>
       </c>
       <c r="B2" s="5" t="s">
         <v>18</v>
       </c>
-      <c r="C2" s="15" t="s">
+      <c r="C2" s="6" t="s">
         <v>1</v>
       </c>
       <c r="D2" s="6" t="s">
         <v>18</v>
       </c>
-      <c r="F2" s="14" t="s">
+      <c r="F2" s="5" t="s">
         <v>0</v>
       </c>
       <c r="G2" s="5" t="s">
         <v>18</v>
       </c>
-      <c r="H2" s="15" t="s">
+      <c r="H2" s="6" t="s">
         <v>1</v>
       </c>
       <c r="I2" s="6" t="s">
         <v>18</v>
       </c>
-      <c r="K2" s="14" t="s">
+      <c r="K2" s="5" t="s">
         <v>0</v>
       </c>
       <c r="L2" s="5" t="s">
         <v>18</v>
       </c>
-      <c r="M2" s="15" t="s">
+      <c r="M2" s="6" t="s">
         <v>1</v>
       </c>
       <c r="N2" s="6" t="s">
         <v>18</v>
       </c>
-      <c r="P2" s="14" t="s">
+      <c r="P2" s="5" t="s">
         <v>0</v>
       </c>
       <c r="Q2" s="5" t="s">
         <v>18</v>
       </c>
-      <c r="R2" s="15" t="s">
+      <c r="R2" s="6" t="s">
         <v>1</v>
       </c>
       <c r="S2" s="6" t="s">
         <v>18</v>
       </c>
-      <c r="U2" s="14" t="s">
+      <c r="U2" s="5" t="s">
         <v>0</v>
       </c>
       <c r="V2" s="5" t="s">
         <v>18</v>
       </c>
-      <c r="W2" s="15" t="s">
+      <c r="W2" s="6" t="s">
         <v>1</v>
       </c>
       <c r="X2" s="6" t="s">
         <v>18</v>
       </c>
+      <c r="Z2" s="5" t="s">
+        <v>0</v>
+      </c>
+      <c r="AA2" s="5" t="s">
+        <v>18</v>
+      </c>
+      <c r="AB2" s="6" t="s">
+        <v>1</v>
+      </c>
+      <c r="AC2" s="6" t="s">
+        <v>18</v>
+      </c>
+      <c r="AE2" s="5" t="s">
+        <v>0</v>
+      </c>
+      <c r="AF2" s="5" t="s">
+        <v>18</v>
+      </c>
+      <c r="AG2" s="6" t="s">
+        <v>1</v>
+      </c>
+      <c r="AH2" s="6" t="s">
+        <v>18</v>
+      </c>
     </row>
-    <row r="3" spans="1:24" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A3" s="10" t="s">
+    <row r="3" spans="1:34" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A3" s="11" t="s">
         <v>3</v>
       </c>
       <c r="B3" s="8" t="s">
         <v>2</v>
       </c>
-      <c r="C3" s="12" t="s">
+      <c r="C3" s="10" t="s">
         <v>26</v>
       </c>
       <c r="D3" s="9" t="s">
         <v>2</v>
       </c>
-      <c r="F3" s="10" t="s">
+      <c r="F3" s="11" t="s">
         <v>3</v>
       </c>
       <c r="G3" s="8" t="s">
         <v>2</v>
       </c>
-      <c r="H3" s="12" t="s">
+      <c r="H3" s="10" t="s">
         <v>23</v>
       </c>
       <c r="I3" s="9" t="s">
         <v>2</v>
       </c>
-      <c r="K3" s="10" t="s">
+      <c r="K3" s="11" t="s">
         <v>28</v>
       </c>
       <c r="L3" s="8" t="s">
         <v>2</v>
       </c>
-      <c r="M3" s="12" t="s">
+      <c r="M3" s="10" t="s">
         <v>23</v>
       </c>
       <c r="N3" s="9" t="s">
         <v>2</v>
       </c>
-      <c r="P3" s="10" t="s">
+      <c r="P3" s="11" t="s">
         <v>3</v>
       </c>
       <c r="Q3" s="8" t="s">
         <v>2</v>
       </c>
-      <c r="R3" s="12" t="s">
+      <c r="R3" s="10" t="s">
         <v>23</v>
       </c>
       <c r="S3" s="9" t="s">
         <v>2</v>
       </c>
-      <c r="U3" s="10" t="s">
+      <c r="U3" s="11" t="s">
         <v>32</v>
       </c>
       <c r="V3" s="8" t="s">
         <v>2</v>
       </c>
-      <c r="W3" s="12" t="s">
+      <c r="W3" s="10" t="s">
         <v>23</v>
       </c>
       <c r="X3" s="9" t="s">
         <v>2</v>
       </c>
+      <c r="Z3" s="11" t="s">
+        <v>36</v>
+      </c>
+      <c r="AA3" s="8" t="s">
+        <v>2</v>
+      </c>
+      <c r="AB3" s="10" t="s">
+        <v>23</v>
+      </c>
+      <c r="AC3" s="9" t="s">
+        <v>2</v>
+      </c>
+      <c r="AE3" s="11" t="s">
+        <v>39</v>
+      </c>
+      <c r="AF3" s="8" t="s">
+        <v>2</v>
+      </c>
+      <c r="AG3" s="10" t="s">
+        <v>23</v>
+      </c>
+      <c r="AH3" s="9" t="s">
+        <v>2</v>
+      </c>
     </row>
-    <row r="4" spans="1:24" x14ac:dyDescent="0.25">
-      <c r="A4" s="11" t="s">
+    <row r="4" spans="1:34" x14ac:dyDescent="0.25">
+      <c r="A4" s="4" t="s">
         <v>4</v>
       </c>
       <c r="B4" s="4"/>
-      <c r="C4" s="13" t="s">
+      <c r="C4" s="3" t="s">
         <v>21</v>
       </c>
       <c r="D4" s="3"/>
-      <c r="F4" s="11" t="s">
+      <c r="F4" s="4" t="s">
         <v>12</v>
       </c>
       <c r="G4" s="4"/>
-      <c r="H4" s="13" t="s">
+      <c r="H4" s="3" t="s">
         <v>13</v>
       </c>
       <c r="I4" s="3"/>
-      <c r="K4" s="11" t="s">
+      <c r="K4" s="4" t="s">
         <v>12</v>
       </c>
       <c r="L4" s="4"/>
-      <c r="M4" s="13" t="s">
+      <c r="M4" s="3" t="s">
         <v>13</v>
       </c>
       <c r="N4" s="3"/>
-      <c r="P4" s="11" t="s">
+      <c r="P4" s="4" t="s">
         <v>30</v>
       </c>
       <c r="Q4" s="4"/>
-      <c r="R4" s="13" t="s">
+      <c r="R4" s="3" t="s">
         <v>13</v>
       </c>
       <c r="S4" s="3"/>
-      <c r="U4" s="11" t="s">
+      <c r="U4" s="4" t="s">
         <v>30</v>
       </c>
       <c r="V4" s="4"/>
-      <c r="W4" s="13" t="s">
+      <c r="W4" s="3" t="s">
         <v>13</v>
       </c>
       <c r="X4" s="3"/>
+      <c r="Z4" s="4" t="s">
+        <v>30</v>
+      </c>
+      <c r="AA4" s="4"/>
+      <c r="AB4" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="AC4" s="3">
+        <v>1</v>
+      </c>
+      <c r="AE4" s="4" t="s">
+        <v>12</v>
+      </c>
+      <c r="AF4" s="4"/>
+      <c r="AG4" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="AH4" s="3"/>
     </row>
-    <row r="5" spans="1:24" x14ac:dyDescent="0.25">
-      <c r="A5" s="11" t="s">
+    <row r="5" spans="1:34" x14ac:dyDescent="0.25">
+      <c r="A5" s="4" t="s">
         <v>5</v>
       </c>
       <c r="B5" s="4">
         <v>1</v>
       </c>
-      <c r="C5" s="13" t="s">
+      <c r="C5" s="3" t="s">
         <v>12</v>
       </c>
       <c r="D5" s="3">
         <v>2</v>
       </c>
-      <c r="F5" s="11" t="s">
+      <c r="F5" s="4" t="s">
         <v>21</v>
       </c>
       <c r="G5" s="4"/>
-      <c r="H5" s="13" t="s">
+      <c r="H5" s="3" t="s">
         <v>14</v>
       </c>
       <c r="I5" s="3">
         <v>1</v>
       </c>
-      <c r="K5" s="11" t="s">
+      <c r="K5" s="4" t="s">
         <v>24</v>
       </c>
       <c r="L5" s="4">
         <v>2</v>
       </c>
-      <c r="M5" s="13" t="s">
+      <c r="M5" s="3" t="s">
         <v>14</v>
       </c>
       <c r="N5" s="3">
         <v>3</v>
       </c>
-      <c r="P5" s="11" t="s">
+      <c r="P5" s="4" t="s">
         <v>24</v>
       </c>
       <c r="Q5" s="4">
         <v>3</v>
       </c>
-      <c r="R5" s="13" t="s">
+      <c r="R5" s="3" t="s">
         <v>14</v>
       </c>
       <c r="S5" s="3">
         <v>4</v>
       </c>
-      <c r="U5" s="11" t="s">
+      <c r="U5" s="4" t="s">
         <v>24</v>
       </c>
       <c r="V5" s="4"/>
-      <c r="W5" s="13" t="s">
+      <c r="W5" s="3" t="s">
         <v>14</v>
       </c>
       <c r="X5" s="3"/>
+      <c r="Z5" s="4" t="s">
+        <v>29</v>
+      </c>
+      <c r="AA5" s="4">
+        <v>1</v>
+      </c>
+      <c r="AB5" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="AC5" s="3"/>
+      <c r="AE5" s="4" t="s">
+        <v>30</v>
+      </c>
+      <c r="AF5" s="4"/>
+      <c r="AG5" s="3" t="s">
+        <v>14</v>
+      </c>
+      <c r="AH5" s="3"/>
     </row>
-    <row r="6" spans="1:24" x14ac:dyDescent="0.25">
-      <c r="A6" s="11" t="s">
+    <row r="6" spans="1:34" x14ac:dyDescent="0.25">
+      <c r="A6" s="4" t="s">
         <v>6</v>
       </c>
       <c r="B6" s="4">
         <v>1</v>
       </c>
-      <c r="C6" s="13" t="s">
+      <c r="C6" s="3" t="s">
         <v>13</v>
       </c>
       <c r="D6" s="3"/>
-      <c r="F6" s="11" t="s">
+      <c r="F6" s="4" t="s">
         <v>7</v>
       </c>
       <c r="G6" s="4">
         <v>1</v>
       </c>
-      <c r="H6" s="13" t="s">
+      <c r="H6" s="3" t="s">
         <v>24</v>
       </c>
       <c r="I6" s="3">
         <v>3</v>
       </c>
-      <c r="K6" s="11" t="s">
+      <c r="K6" s="4" t="s">
         <v>7</v>
       </c>
       <c r="L6" s="4">
         <v>1</v>
       </c>
-      <c r="M6" s="13" t="s">
+      <c r="M6" s="3" t="s">
         <v>21</v>
       </c>
       <c r="N6" s="3"/>
-      <c r="P6" s="11" t="s">
+      <c r="P6" s="4" t="s">
         <v>7</v>
       </c>
       <c r="Q6" s="4">
         <v>4</v>
       </c>
-      <c r="R6" s="13" t="s">
+      <c r="R6" s="3" t="s">
         <v>29</v>
       </c>
       <c r="S6" s="3">
         <v>4</v>
       </c>
-      <c r="U6" s="11" t="s">
+      <c r="U6" s="4" t="s">
         <v>15</v>
       </c>
       <c r="V6" s="4">
         <v>1</v>
       </c>
-      <c r="W6" s="13" t="s">
+      <c r="W6" s="3" t="s">
         <v>12</v>
       </c>
       <c r="X6" s="3">
         <v>1</v>
       </c>
+      <c r="Z6" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="AA6" s="4"/>
+      <c r="AB6" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="AC6" s="3"/>
+      <c r="AE6" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="AF6" s="4">
+        <v>2</v>
+      </c>
+      <c r="AG6" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="AH6" s="3"/>
     </row>
-    <row r="7" spans="1:24" x14ac:dyDescent="0.25">
-      <c r="A7" s="11" t="s">
+    <row r="7" spans="1:34" x14ac:dyDescent="0.25">
+      <c r="A7" s="4" t="s">
         <v>7</v>
       </c>
       <c r="B7" s="4">
         <v>1</v>
       </c>
-      <c r="C7" s="13" t="s">
+      <c r="C7" s="3" t="s">
         <v>14</v>
       </c>
       <c r="D7" s="3">
         <v>1</v>
       </c>
-      <c r="F7" s="11" t="s">
+      <c r="F7" s="4" t="s">
         <v>6</v>
       </c>
       <c r="G7" s="4">
         <v>2</v>
       </c>
-      <c r="H7" s="13" t="s">
+      <c r="H7" s="3" t="s">
         <v>25</v>
       </c>
       <c r="I7" s="3"/>
-      <c r="K7" s="11" t="s">
+      <c r="K7" s="4" t="s">
         <v>16</v>
       </c>
       <c r="L7" s="4">
         <v>1</v>
       </c>
-      <c r="M7" s="13" t="s">
+      <c r="M7" s="3" t="s">
         <v>5</v>
       </c>
       <c r="N7" s="3"/>
-      <c r="P7" s="11" t="s">
+      <c r="P7" s="4" t="s">
         <v>5</v>
       </c>
       <c r="Q7" s="4"/>
-      <c r="R7" s="13" t="s">
+      <c r="R7" s="3" t="s">
         <v>8</v>
       </c>
       <c r="S7" s="3"/>
-      <c r="U7" s="11" t="s">
+      <c r="U7" s="4" t="s">
         <v>5</v>
       </c>
       <c r="V7" s="4">
         <v>1</v>
       </c>
-      <c r="W7" s="13" t="s">
+      <c r="W7" s="3" t="s">
         <v>34</v>
       </c>
       <c r="X7" s="3">
         <v>2</v>
       </c>
+      <c r="Z7" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="AA7" s="4">
+        <v>3</v>
+      </c>
+      <c r="AB7" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="AC7" s="3"/>
+      <c r="AE7" s="4" t="s">
+        <v>35</v>
+      </c>
+      <c r="AF7" s="4"/>
+      <c r="AG7" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="AH7" s="3">
+        <v>4</v>
+      </c>
     </row>
-    <row r="8" spans="1:24" x14ac:dyDescent="0.25">
-      <c r="A8" s="11" t="s">
+    <row r="8" spans="1:34" x14ac:dyDescent="0.25">
+      <c r="A8" s="4" t="s">
         <v>8</v>
       </c>
       <c r="B8" s="4"/>
-      <c r="C8" s="13" t="s">
+      <c r="C8" s="3" t="s">
         <v>15</v>
       </c>
       <c r="D8" s="3">
         <v>3</v>
       </c>
-      <c r="F8" s="11" t="s">
+      <c r="F8" s="4" t="s">
         <v>5</v>
       </c>
       <c r="G8" s="4">
         <v>2</v>
       </c>
-      <c r="H8" s="13" t="s">
+      <c r="H8" s="3" t="s">
         <v>16</v>
       </c>
       <c r="I8" s="3">
         <v>1</v>
       </c>
-      <c r="K8" s="11" t="s">
+      <c r="K8" s="4" t="s">
         <v>10</v>
       </c>
       <c r="L8" s="4"/>
-      <c r="M8" s="13" t="s">
+      <c r="M8" s="3" t="s">
         <v>17</v>
       </c>
       <c r="N8" s="3"/>
-      <c r="P8" s="11" t="s">
+      <c r="P8" s="4" t="s">
         <v>31</v>
       </c>
       <c r="Q8" s="4"/>
-      <c r="R8" s="13" t="s">
+      <c r="R8" s="3" t="s">
         <v>16</v>
       </c>
       <c r="S8" s="3">
         <v>1</v>
       </c>
-      <c r="U8" s="11" t="s">
+      <c r="U8" s="4" t="s">
         <v>16</v>
       </c>
       <c r="V8" s="4">
         <v>1</v>
       </c>
-      <c r="W8" s="13" t="s">
+      <c r="W8" s="3" t="s">
         <v>7</v>
       </c>
       <c r="X8" s="3">
         <v>2</v>
       </c>
+      <c r="Z8" s="4" t="s">
+        <v>5</v>
+      </c>
+      <c r="AA8" s="4">
+        <v>2</v>
+      </c>
+      <c r="AB8" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="AC8" s="3">
+        <v>1</v>
+      </c>
+      <c r="AE8" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="AF8" s="4">
+        <v>1</v>
+      </c>
+      <c r="AG8" s="3" t="s">
+        <v>38</v>
+      </c>
+      <c r="AH8" s="3">
+        <v>1</v>
+      </c>
     </row>
-    <row r="9" spans="1:24" x14ac:dyDescent="0.25">
-      <c r="A9" s="11" t="s">
+    <row r="9" spans="1:34" x14ac:dyDescent="0.25">
+      <c r="A9" s="4" t="s">
         <v>10</v>
       </c>
       <c r="B9" s="4">
         <v>1</v>
       </c>
-      <c r="C9" s="13" t="s">
+      <c r="C9" s="3" t="s">
         <v>16</v>
       </c>
       <c r="D9" s="3"/>
-      <c r="F9" s="11" t="s">
+      <c r="F9" s="4" t="s">
         <v>10</v>
       </c>
       <c r="G9" s="4"/>
-      <c r="H9" s="13" t="s">
+      <c r="H9" s="3" t="s">
         <v>15</v>
       </c>
       <c r="I9" s="3">
         <v>2</v>
       </c>
-      <c r="K9" s="11" t="s">
+      <c r="K9" s="4" t="s">
         <v>8</v>
       </c>
       <c r="L9" s="4"/>
-      <c r="M9" s="13" t="s">
+      <c r="M9" s="3" t="s">
         <v>6</v>
       </c>
       <c r="N9" s="3">
         <v>1</v>
       </c>
-      <c r="P9" s="11" t="s">
+      <c r="P9" s="4" t="s">
         <v>10</v>
       </c>
       <c r="Q9" s="4">
         <v>1</v>
       </c>
-      <c r="R9" s="13" t="s">
+      <c r="R9" s="3" t="s">
         <v>15</v>
       </c>
       <c r="S9" s="3">
         <v>3</v>
       </c>
-      <c r="U9" s="11" t="s">
+      <c r="U9" s="4" t="s">
         <v>33</v>
       </c>
       <c r="V9" s="4">
         <v>1</v>
       </c>
-      <c r="W9" s="13" t="s">
+      <c r="W9" s="3" t="s">
         <v>6</v>
       </c>
       <c r="X9" s="3"/>
+      <c r="Z9" s="4" t="s">
+        <v>35</v>
+      </c>
+      <c r="AA9" s="4">
+        <v>2</v>
+      </c>
+      <c r="AB9" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="AC9" s="3">
+        <v>1</v>
+      </c>
+      <c r="AE9" s="4" t="s">
+        <v>37</v>
+      </c>
+      <c r="AF9" s="4">
+        <v>2</v>
+      </c>
+      <c r="AG9" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="AH9" s="3">
+        <v>2</v>
+      </c>
     </row>
-    <row r="10" spans="1:24" x14ac:dyDescent="0.25">
-      <c r="A10" s="11" t="s">
+    <row r="10" spans="1:34" x14ac:dyDescent="0.25">
+      <c r="A10" s="4" t="s">
         <v>11</v>
       </c>
       <c r="B10" s="4">
         <v>1</v>
       </c>
-      <c r="C10" s="13" t="s">
+      <c r="C10" s="3" t="s">
         <v>17</v>
       </c>
       <c r="D10" s="3">
         <v>1</v>
       </c>
-      <c r="F10" s="11" t="s">
+      <c r="F10" s="4" t="s">
         <v>11</v>
       </c>
       <c r="G10" s="4"/>
-      <c r="H10" s="13"/>
+      <c r="H10" s="3"/>
       <c r="I10" s="3"/>
-      <c r="K10" s="11" t="s">
+      <c r="K10" s="4" t="s">
         <v>27</v>
       </c>
       <c r="L10" s="4">
         <v>2</v>
       </c>
-      <c r="M10" s="13" t="s">
+      <c r="M10" s="3" t="s">
         <v>15</v>
       </c>
       <c r="N10" s="3">
         <v>1</v>
       </c>
-      <c r="P10" s="11" t="s">
+      <c r="P10" s="4" t="s">
         <v>6</v>
       </c>
       <c r="Q10" s="4">
         <v>2</v>
       </c>
-      <c r="R10" s="13" t="s">
+      <c r="R10" s="3" t="s">
         <v>9</v>
       </c>
       <c r="S10" s="3">
         <v>3</v>
       </c>
-      <c r="U10" s="11" t="s">
+      <c r="U10" s="4" t="s">
         <v>9</v>
       </c>
       <c r="V10" s="4">
         <v>1</v>
       </c>
-      <c r="W10" s="13" t="s">
+      <c r="W10" s="3" t="s">
         <v>35</v>
       </c>
       <c r="X10" s="3">
         <v>1</v>
       </c>
+      <c r="Z10" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="AA10" s="4">
+        <v>1</v>
+      </c>
+      <c r="AB10" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="AC10" s="3">
+        <v>2</v>
+      </c>
+      <c r="AE10" s="4" t="s">
+        <v>5</v>
+      </c>
+      <c r="AF10" s="4">
+        <v>2</v>
+      </c>
+      <c r="AG10" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="AH10" s="3">
+        <v>4</v>
+      </c>
     </row>
-    <row r="11" spans="1:24" x14ac:dyDescent="0.25">
-      <c r="A11" s="11" t="s">
+    <row r="11" spans="1:34" x14ac:dyDescent="0.25">
+      <c r="A11" s="4" t="s">
         <v>9</v>
       </c>
       <c r="B11" s="4">
         <v>3</v>
       </c>
-      <c r="C11" s="13"/>
+      <c r="C11" s="3"/>
       <c r="D11" s="3"/>
-      <c r="F11" s="11" t="s">
+      <c r="F11" s="4" t="s">
         <v>9</v>
       </c>
       <c r="G11" s="4"/>
-      <c r="H11" s="13"/>
+      <c r="H11" s="3"/>
       <c r="I11" s="3"/>
-      <c r="K11" s="11" t="s">
+      <c r="K11" s="4" t="s">
         <v>11</v>
       </c>
       <c r="L11" s="4">
         <v>1</v>
       </c>
-      <c r="M11" s="13" t="s">
+      <c r="M11" s="3" t="s">
         <v>9</v>
       </c>
       <c r="N11" s="3">
         <v>1</v>
       </c>
-      <c r="P11" s="11" t="s">
+      <c r="P11" s="4" t="s">
         <v>11</v>
       </c>
       <c r="Q11" s="4"/>
-      <c r="R11" s="13"/>
+      <c r="R11" s="3"/>
       <c r="S11" s="3"/>
-      <c r="U11" s="11"/>
+      <c r="U11" s="4"/>
       <c r="V11" s="4"/>
-      <c r="W11" s="13"/>
+      <c r="W11" s="3"/>
       <c r="X11" s="3"/>
+      <c r="Z11" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="AA11" s="4">
+        <v>1</v>
+      </c>
+      <c r="AB11" s="3"/>
+      <c r="AC11" s="3"/>
+      <c r="AE11" s="4"/>
+      <c r="AF11" s="4"/>
+      <c r="AG11" s="3"/>
+      <c r="AH11" s="3"/>
     </row>
-    <row r="12" spans="1:24" x14ac:dyDescent="0.25">
-      <c r="A12" s="11"/>
+    <row r="12" spans="1:34" x14ac:dyDescent="0.25">
+      <c r="A12" s="4"/>
       <c r="B12" s="4"/>
-      <c r="C12" s="13"/>
+      <c r="C12" s="3"/>
       <c r="D12" s="3"/>
-      <c r="F12" s="11"/>
+      <c r="F12" s="4"/>
       <c r="G12" s="4"/>
-      <c r="H12" s="13"/>
+      <c r="H12" s="3"/>
       <c r="I12" s="3"/>
-      <c r="K12" s="11" t="s">
+      <c r="K12" s="4" t="s">
         <v>6</v>
       </c>
       <c r="L12" s="4">
         <v>1</v>
       </c>
-      <c r="M12" s="13"/>
+      <c r="M12" s="3"/>
       <c r="N12" s="3"/>
-      <c r="P12" s="11"/>
+      <c r="P12" s="4"/>
       <c r="Q12" s="4"/>
-      <c r="R12" s="13"/>
+      <c r="R12" s="3"/>
       <c r="S12" s="3"/>
-      <c r="U12" s="11"/>
+      <c r="U12" s="4"/>
       <c r="V12" s="4"/>
-      <c r="W12" s="13"/>
+      <c r="W12" s="3"/>
       <c r="X12" s="3"/>
+      <c r="Z12" s="4"/>
+      <c r="AA12" s="4"/>
+      <c r="AB12" s="3"/>
+      <c r="AC12" s="3"/>
+      <c r="AE12" s="4"/>
+      <c r="AF12" s="4"/>
+      <c r="AG12" s="3"/>
+      <c r="AH12" s="3"/>
     </row>
-    <row r="13" spans="1:24" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:34" x14ac:dyDescent="0.25">
       <c r="A13" s="7" t="s">
         <v>19</v>
       </c>
@@ -1387,6 +1626,34 @@
       <c r="X13" s="7">
         <f>SUM(X2:X12)</f>
         <v>6</v>
+      </c>
+      <c r="Z13" s="7" t="s">
+        <v>19</v>
+      </c>
+      <c r="AA13" s="7">
+        <f>SUM(AA2:AA12)</f>
+        <v>10</v>
+      </c>
+      <c r="AB13" s="7" t="s">
+        <v>22</v>
+      </c>
+      <c r="AC13" s="7">
+        <f>SUM(AC2:AC12)</f>
+        <v>5</v>
+      </c>
+      <c r="AE13" s="7" t="s">
+        <v>19</v>
+      </c>
+      <c r="AF13" s="7">
+        <f>SUM(AF2:AF12)</f>
+        <v>7</v>
+      </c>
+      <c r="AG13" s="7" t="s">
+        <v>22</v>
+      </c>
+      <c r="AH13" s="7">
+        <f>SUM(AH2:AH12)</f>
+        <v>11</v>
       </c>
     </row>
   </sheetData>

--- a/FCT.xlsx
+++ b/FCT.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/cc257be1a5798d86/WILLIAN/FCT Terça/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="212" documentId="13_ncr:1_{4721CD4C-DC5B-4D56-86E7-BD97B97F13DF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{8F1CCDF9-D84F-44C7-BFB8-DC747D9D1464}"/>
+  <xr:revisionPtr revIDLastSave="242" documentId="13_ncr:1_{4721CD4C-DC5B-4D56-86E7-BD97B97F13DF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{89CC10DA-E3B4-4EFB-8BEC-C39F14F61EF0}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{4C5D2070-0CD2-4A2B-85DD-4C1228673220}"/>
   </bookViews>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="181" uniqueCount="40">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="205" uniqueCount="40">
   <si>
     <t>Azul</t>
   </si>
@@ -690,7 +690,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8E481E65-1F7A-4C5C-8819-A9B2DFE6B944}">
-  <dimension ref="A1:AH13"/>
+  <dimension ref="A1:AM13"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="2" width="9.140625" style="1"/>
@@ -719,10 +719,12 @@
     <col min="31" max="31" width="11.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="32" max="32" width="9.140625" style="1"/>
     <col min="33" max="33" width="11.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="34" max="16384" width="9.140625" style="1"/>
+    <col min="34" max="37" width="9.140625" style="1"/>
+    <col min="38" max="38" width="12.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="39" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:34" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:39" x14ac:dyDescent="0.25">
       <c r="A1" s="2"/>
       <c r="B1" s="2" t="s">
         <v>20</v>
@@ -779,8 +781,16 @@
         <v>46280</v>
       </c>
       <c r="AH1" s="2"/>
+      <c r="AJ1" s="2"/>
+      <c r="AK1" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="AL1" s="2">
+        <v>46287</v>
+      </c>
+      <c r="AM1" s="2"/>
     </row>
-    <row r="2" spans="1:34" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:39" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A2" s="5" t="s">
         <v>0</v>
       </c>
@@ -865,8 +875,20 @@
       <c r="AH2" s="6" t="s">
         <v>18</v>
       </c>
+      <c r="AJ2" s="5" t="s">
+        <v>0</v>
+      </c>
+      <c r="AK2" s="5" t="s">
+        <v>18</v>
+      </c>
+      <c r="AL2" s="6" t="s">
+        <v>1</v>
+      </c>
+      <c r="AM2" s="6" t="s">
+        <v>18</v>
+      </c>
     </row>
-    <row r="3" spans="1:34" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:39" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A3" s="11" t="s">
         <v>3</v>
       </c>
@@ -951,8 +973,18 @@
       <c r="AH3" s="9" t="s">
         <v>2</v>
       </c>
+      <c r="AJ3" s="11" t="s">
+        <v>23</v>
+      </c>
+      <c r="AK3" s="8" t="s">
+        <v>2</v>
+      </c>
+      <c r="AL3" s="10"/>
+      <c r="AM3" s="9" t="s">
+        <v>2</v>
+      </c>
     </row>
-    <row r="4" spans="1:34" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:39" x14ac:dyDescent="0.25">
       <c r="A4" s="4" t="s">
         <v>4</v>
       </c>
@@ -1011,8 +1043,16 @@
         <v>13</v>
       </c>
       <c r="AH4" s="3"/>
+      <c r="AJ4" s="4" t="s">
+        <v>30</v>
+      </c>
+      <c r="AK4" s="4"/>
+      <c r="AL4" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="AM4" s="3"/>
     </row>
-    <row r="5" spans="1:34" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:39" x14ac:dyDescent="0.25">
       <c r="A5" s="4" t="s">
         <v>5</v>
       </c>
@@ -1085,8 +1125,20 @@
         <v>14</v>
       </c>
       <c r="AH5" s="3"/>
+      <c r="AJ5" s="4" t="s">
+        <v>24</v>
+      </c>
+      <c r="AK5" s="4">
+        <v>1</v>
+      </c>
+      <c r="AL5" s="3" t="s">
+        <v>14</v>
+      </c>
+      <c r="AM5" s="3">
+        <v>2</v>
+      </c>
     </row>
-    <row r="6" spans="1:34" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:39" x14ac:dyDescent="0.25">
       <c r="A6" s="4" t="s">
         <v>6</v>
       </c>
@@ -1161,8 +1213,18 @@
         <v>24</v>
       </c>
       <c r="AH6" s="3"/>
+      <c r="AJ6" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="AK6" s="4">
+        <v>1</v>
+      </c>
+      <c r="AL6" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="AM6" s="3"/>
     </row>
-    <row r="7" spans="1:34" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:39" x14ac:dyDescent="0.25">
       <c r="A7" s="4" t="s">
         <v>7</v>
       </c>
@@ -1235,8 +1297,18 @@
       <c r="AH7" s="3">
         <v>4</v>
       </c>
+      <c r="AJ7" s="4" t="s">
+        <v>8</v>
+      </c>
+      <c r="AK7" s="4">
+        <v>1</v>
+      </c>
+      <c r="AL7" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="AM7" s="3"/>
     </row>
-    <row r="8" spans="1:34" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:39" x14ac:dyDescent="0.25">
       <c r="A8" s="4" t="s">
         <v>8</v>
       </c>
@@ -1313,8 +1385,20 @@
       <c r="AH8" s="3">
         <v>1</v>
       </c>
+      <c r="AJ8" s="4" t="s">
+        <v>16</v>
+      </c>
+      <c r="AK8" s="4">
+        <v>1</v>
+      </c>
+      <c r="AL8" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="AM8" s="3">
+        <v>1</v>
+      </c>
     </row>
-    <row r="9" spans="1:34" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:39" x14ac:dyDescent="0.25">
       <c r="A9" s="4" t="s">
         <v>10</v>
       </c>
@@ -1391,8 +1475,18 @@
       <c r="AH9" s="3">
         <v>2</v>
       </c>
+      <c r="AJ9" s="4" t="s">
+        <v>38</v>
+      </c>
+      <c r="AK9" s="4">
+        <v>2</v>
+      </c>
+      <c r="AL9" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="AM9" s="3"/>
     </row>
-    <row r="10" spans="1:34" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:39" x14ac:dyDescent="0.25">
       <c r="A10" s="4" t="s">
         <v>11</v>
       </c>
@@ -1471,8 +1565,20 @@
       <c r="AH10" s="3">
         <v>4</v>
       </c>
+      <c r="AJ10" s="4" t="s">
+        <v>27</v>
+      </c>
+      <c r="AK10" s="4">
+        <v>6</v>
+      </c>
+      <c r="AL10" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="AM10" s="3">
+        <v>2</v>
+      </c>
     </row>
-    <row r="11" spans="1:34" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:39" x14ac:dyDescent="0.25">
       <c r="A11" s="4" t="s">
         <v>9</v>
       </c>
@@ -1521,8 +1627,12 @@
       <c r="AF11" s="4"/>
       <c r="AG11" s="3"/>
       <c r="AH11" s="3"/>
+      <c r="AJ11" s="4"/>
+      <c r="AK11" s="4"/>
+      <c r="AL11" s="3"/>
+      <c r="AM11" s="3"/>
     </row>
-    <row r="12" spans="1:34" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:39" x14ac:dyDescent="0.25">
       <c r="A12" s="4"/>
       <c r="B12" s="4"/>
       <c r="C12" s="3"/>
@@ -1555,8 +1665,12 @@
       <c r="AF12" s="4"/>
       <c r="AG12" s="3"/>
       <c r="AH12" s="3"/>
+      <c r="AJ12" s="4"/>
+      <c r="AK12" s="4"/>
+      <c r="AL12" s="3"/>
+      <c r="AM12" s="3"/>
     </row>
-    <row r="13" spans="1:34" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:39" x14ac:dyDescent="0.25">
       <c r="A13" s="7" t="s">
         <v>19</v>
       </c>
@@ -1654,6 +1768,20 @@
       <c r="AH13" s="7">
         <f>SUM(AH2:AH12)</f>
         <v>11</v>
+      </c>
+      <c r="AJ13" s="7" t="s">
+        <v>19</v>
+      </c>
+      <c r="AK13" s="7">
+        <f>SUM(AK2:AK12)</f>
+        <v>12</v>
+      </c>
+      <c r="AL13" s="7" t="s">
+        <v>22</v>
+      </c>
+      <c r="AM13" s="7">
+        <f>SUM(AM2:AM12)</f>
+        <v>5</v>
       </c>
     </row>
   </sheetData>

--- a/FCT.xlsx
+++ b/FCT.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/cc257be1a5798d86/WILLIAN/FCT Terça/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="242" documentId="13_ncr:1_{4721CD4C-DC5B-4D56-86E7-BD97B97F13DF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{89CC10DA-E3B4-4EFB-8BEC-C39F14F61EF0}"/>
+  <xr:revisionPtr revIDLastSave="243" documentId="13_ncr:1_{4721CD4C-DC5B-4D56-86E7-BD97B97F13DF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{083AD0F1-0C18-489D-9F35-1281257DD41C}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{4C5D2070-0CD2-4A2B-85DD-4C1228673220}"/>
   </bookViews>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="205" uniqueCount="40">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="206" uniqueCount="41">
   <si>
     <t>Azul</t>
   </si>
@@ -159,6 +159,9 @@
   </si>
   <si>
     <t>Volber</t>
+  </si>
+  <si>
+    <t>Fábio Rosa</t>
   </si>
 </sst>
 </file>
@@ -979,7 +982,9 @@
       <c r="AK3" s="8" t="s">
         <v>2</v>
       </c>
-      <c r="AL3" s="10"/>
+      <c r="AL3" s="10" t="s">
+        <v>40</v>
+      </c>
       <c r="AM3" s="9" t="s">
         <v>2</v>
       </c>

--- a/FCT.xlsx
+++ b/FCT.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30326"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30430"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/cc257be1a5798d86/WILLIAN/FCT Terça/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="243" documentId="13_ncr:1_{4721CD4C-DC5B-4D56-86E7-BD97B97F13DF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{083AD0F1-0C18-489D-9F35-1281257DD41C}"/>
+  <xr:revisionPtr revIDLastSave="264" documentId="13_ncr:1_{4721CD4C-DC5B-4D56-86E7-BD97B97F13DF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{155E737B-CB46-4637-98DD-97EA6904B4BF}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{4C5D2070-0CD2-4A2B-85DD-4C1228673220}"/>
   </bookViews>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="206" uniqueCount="41">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="232" uniqueCount="41">
   <si>
     <t>Azul</t>
   </si>
@@ -693,7 +693,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8E481E65-1F7A-4C5C-8819-A9B2DFE6B944}">
-  <dimension ref="A1:AM13"/>
+  <dimension ref="A1:AR13"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="2" width="9.140625" style="1"/>
@@ -724,10 +724,14 @@
     <col min="33" max="33" width="11.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="34" max="37" width="9.140625" style="1"/>
     <col min="38" max="38" width="12.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="39" max="16384" width="9.140625" style="1"/>
+    <col min="39" max="40" width="9.140625" style="1"/>
+    <col min="41" max="41" width="11.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="42" max="42" width="9.140625" style="1"/>
+    <col min="43" max="43" width="12.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="44" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:39" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:44" x14ac:dyDescent="0.25">
       <c r="A1" s="2"/>
       <c r="B1" s="2" t="s">
         <v>20</v>
@@ -792,8 +796,16 @@
         <v>46287</v>
       </c>
       <c r="AM1" s="2"/>
+      <c r="AO1" s="2"/>
+      <c r="AP1" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="AQ1" s="2">
+        <v>46301</v>
+      </c>
+      <c r="AR1" s="2"/>
     </row>
-    <row r="2" spans="1:39" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:44" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A2" s="5" t="s">
         <v>0</v>
       </c>
@@ -890,8 +902,20 @@
       <c r="AM2" s="6" t="s">
         <v>18</v>
       </c>
+      <c r="AO2" s="5" t="s">
+        <v>0</v>
+      </c>
+      <c r="AP2" s="5" t="s">
+        <v>18</v>
+      </c>
+      <c r="AQ2" s="6" t="s">
+        <v>1</v>
+      </c>
+      <c r="AR2" s="6" t="s">
+        <v>18</v>
+      </c>
     </row>
-    <row r="3" spans="1:39" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:44" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A3" s="11" t="s">
         <v>3</v>
       </c>
@@ -988,8 +1012,20 @@
       <c r="AM3" s="9" t="s">
         <v>2</v>
       </c>
+      <c r="AO3" s="11" t="s">
+        <v>23</v>
+      </c>
+      <c r="AP3" s="8" t="s">
+        <v>2</v>
+      </c>
+      <c r="AQ3" s="10" t="s">
+        <v>40</v>
+      </c>
+      <c r="AR3" s="9" t="s">
+        <v>2</v>
+      </c>
     </row>
-    <row r="4" spans="1:39" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:44" x14ac:dyDescent="0.25">
       <c r="A4" s="4" t="s">
         <v>4</v>
       </c>
@@ -1056,8 +1092,16 @@
         <v>13</v>
       </c>
       <c r="AM4" s="3"/>
+      <c r="AO4" s="4" t="s">
+        <v>4</v>
+      </c>
+      <c r="AP4" s="4"/>
+      <c r="AQ4" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="AR4" s="3"/>
     </row>
-    <row r="5" spans="1:39" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:44" x14ac:dyDescent="0.25">
       <c r="A5" s="4" t="s">
         <v>5</v>
       </c>
@@ -1142,8 +1186,16 @@
       <c r="AM5" s="3">
         <v>2</v>
       </c>
+      <c r="AO5" s="4" t="s">
+        <v>12</v>
+      </c>
+      <c r="AP5" s="4"/>
+      <c r="AQ5" s="3" t="s">
+        <v>14</v>
+      </c>
+      <c r="AR5" s="3"/>
     </row>
-    <row r="6" spans="1:39" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:44" x14ac:dyDescent="0.25">
       <c r="A6" s="4" t="s">
         <v>6</v>
       </c>
@@ -1228,8 +1280,16 @@
         <v>12</v>
       </c>
       <c r="AM6" s="3"/>
+      <c r="AO6" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="AP6" s="4"/>
+      <c r="AQ6" s="3" t="s">
+        <v>30</v>
+      </c>
+      <c r="AR6" s="3"/>
     </row>
-    <row r="7" spans="1:39" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:44" x14ac:dyDescent="0.25">
       <c r="A7" s="4" t="s">
         <v>7</v>
       </c>
@@ -1312,8 +1372,18 @@
         <v>7</v>
       </c>
       <c r="AM7" s="3"/>
+      <c r="AO7" s="4" t="s">
+        <v>8</v>
+      </c>
+      <c r="AP7" s="4">
+        <v>2</v>
+      </c>
+      <c r="AQ7" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="AR7" s="3"/>
     </row>
-    <row r="8" spans="1:39" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:44" x14ac:dyDescent="0.25">
       <c r="A8" s="4" t="s">
         <v>8</v>
       </c>
@@ -1402,8 +1472,16 @@
       <c r="AM8" s="3">
         <v>1</v>
       </c>
+      <c r="AO8" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="AP8" s="4"/>
+      <c r="AQ8" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AR8" s="3"/>
     </row>
-    <row r="9" spans="1:39" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:44" x14ac:dyDescent="0.25">
       <c r="A9" s="4" t="s">
         <v>10</v>
       </c>
@@ -1490,8 +1568,20 @@
         <v>17</v>
       </c>
       <c r="AM9" s="3"/>
+      <c r="AO9" s="4" t="s">
+        <v>38</v>
+      </c>
+      <c r="AP9" s="4">
+        <v>4</v>
+      </c>
+      <c r="AQ9" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="AR9" s="3">
+        <v>3</v>
+      </c>
     </row>
-    <row r="10" spans="1:39" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:44" x14ac:dyDescent="0.25">
       <c r="A10" s="4" t="s">
         <v>11</v>
       </c>
@@ -1582,8 +1672,20 @@
       <c r="AM10" s="3">
         <v>2</v>
       </c>
+      <c r="AO10" s="4" t="s">
+        <v>35</v>
+      </c>
+      <c r="AP10" s="4">
+        <v>2</v>
+      </c>
+      <c r="AQ10" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="AR10" s="3">
+        <v>2</v>
+      </c>
     </row>
-    <row r="11" spans="1:39" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:44" x14ac:dyDescent="0.25">
       <c r="A11" s="4" t="s">
         <v>9</v>
       </c>
@@ -1636,8 +1738,14 @@
       <c r="AK11" s="4"/>
       <c r="AL11" s="3"/>
       <c r="AM11" s="3"/>
+      <c r="AO11" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="AP11" s="4"/>
+      <c r="AQ11" s="3"/>
+      <c r="AR11" s="3"/>
     </row>
-    <row r="12" spans="1:39" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:44" x14ac:dyDescent="0.25">
       <c r="A12" s="4"/>
       <c r="B12" s="4"/>
       <c r="C12" s="3"/>
@@ -1674,8 +1782,12 @@
       <c r="AK12" s="4"/>
       <c r="AL12" s="3"/>
       <c r="AM12" s="3"/>
+      <c r="AO12" s="4"/>
+      <c r="AP12" s="4"/>
+      <c r="AQ12" s="3"/>
+      <c r="AR12" s="3"/>
     </row>
-    <row r="13" spans="1:39" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:44" x14ac:dyDescent="0.25">
       <c r="A13" s="7" t="s">
         <v>19</v>
       </c>
@@ -1786,6 +1898,20 @@
       </c>
       <c r="AM13" s="7">
         <f>SUM(AM2:AM12)</f>
+        <v>5</v>
+      </c>
+      <c r="AO13" s="7" t="s">
+        <v>19</v>
+      </c>
+      <c r="AP13" s="7">
+        <f>SUM(AP2:AP12)</f>
+        <v>8</v>
+      </c>
+      <c r="AQ13" s="7" t="s">
+        <v>22</v>
+      </c>
+      <c r="AR13" s="7">
+        <f>SUM(AR2:AR12)</f>
         <v>5</v>
       </c>
     </row>

--- a/FCT.xlsx
+++ b/FCT.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/cc257be1a5798d86/WILLIAN/FCT Terça/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="264" documentId="13_ncr:1_{4721CD4C-DC5B-4D56-86E7-BD97B97F13DF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{155E737B-CB46-4637-98DD-97EA6904B4BF}"/>
+  <xr:revisionPtr revIDLastSave="266" documentId="13_ncr:1_{4721CD4C-DC5B-4D56-86E7-BD97B97F13DF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{454E6D10-F485-4971-B740-66439DC379BB}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{4C5D2070-0CD2-4A2B-85DD-4C1228673220}"/>
   </bookViews>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="232" uniqueCount="41">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="232" uniqueCount="43">
   <si>
     <t>Azul</t>
   </si>
@@ -162,6 +162,12 @@
   </si>
   <si>
     <t>Fábio Rosa</t>
+  </si>
+  <si>
+    <t>Thiago</t>
+  </si>
+  <si>
+    <t>Ricardo</t>
   </si>
 </sst>
 </file>
@@ -1013,13 +1019,13 @@
         <v>2</v>
       </c>
       <c r="AO3" s="11" t="s">
-        <v>23</v>
+        <v>41</v>
       </c>
       <c r="AP3" s="8" t="s">
         <v>2</v>
       </c>
       <c r="AQ3" s="10" t="s">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="AR3" s="9" t="s">
         <v>2</v>

--- a/FCT.xlsx
+++ b/FCT.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/cc257be1a5798d86/WILLIAN/FCT Terça/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="266" documentId="13_ncr:1_{4721CD4C-DC5B-4D56-86E7-BD97B97F13DF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{454E6D10-F485-4971-B740-66439DC379BB}"/>
+  <xr:revisionPtr revIDLastSave="285" documentId="13_ncr:1_{4721CD4C-DC5B-4D56-86E7-BD97B97F13DF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{EEA25F7C-C9B8-43A1-9E1B-5DC5FE06B562}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{4C5D2070-0CD2-4A2B-85DD-4C1228673220}"/>
   </bookViews>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="232" uniqueCount="43">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="258" uniqueCount="45">
   <si>
     <t>Azul</t>
   </si>
@@ -168,6 +168,12 @@
   </si>
   <si>
     <t>Ricardo</t>
+  </si>
+  <si>
+    <t>Fabian</t>
+  </si>
+  <si>
+    <t>Goleiro sem nome</t>
   </si>
 </sst>
 </file>
@@ -699,7 +705,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8E481E65-1F7A-4C5C-8819-A9B2DFE6B944}">
-  <dimension ref="A1:AR13"/>
+  <dimension ref="A1:AW13"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="2" width="9.140625" style="1"/>
@@ -734,10 +740,14 @@
     <col min="41" max="41" width="11.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="42" max="42" width="9.140625" style="1"/>
     <col min="43" max="43" width="12.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="44" max="16384" width="9.140625" style="1"/>
+    <col min="44" max="45" width="9.140625" style="1"/>
+    <col min="46" max="46" width="11.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="47" max="47" width="9.140625" style="1"/>
+    <col min="48" max="48" width="17.28515625" style="1" bestFit="1" customWidth="1"/>
+    <col min="49" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:44" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:49" x14ac:dyDescent="0.25">
       <c r="A1" s="2"/>
       <c r="B1" s="2" t="s">
         <v>20</v>
@@ -810,8 +820,16 @@
         <v>46301</v>
       </c>
       <c r="AR1" s="2"/>
+      <c r="AT1" s="2"/>
+      <c r="AU1" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="AV1" s="2">
+        <v>46308</v>
+      </c>
+      <c r="AW1" s="2"/>
     </row>
-    <row r="2" spans="1:44" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:49" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A2" s="5" t="s">
         <v>0</v>
       </c>
@@ -920,8 +938,20 @@
       <c r="AR2" s="6" t="s">
         <v>18</v>
       </c>
+      <c r="AT2" s="5" t="s">
+        <v>0</v>
+      </c>
+      <c r="AU2" s="5" t="s">
+        <v>18</v>
+      </c>
+      <c r="AV2" s="6" t="s">
+        <v>1</v>
+      </c>
+      <c r="AW2" s="6" t="s">
+        <v>18</v>
+      </c>
     </row>
-    <row r="3" spans="1:44" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:49" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A3" s="11" t="s">
         <v>3</v>
       </c>
@@ -1030,8 +1060,20 @@
       <c r="AR3" s="9" t="s">
         <v>2</v>
       </c>
+      <c r="AT3" s="11" t="s">
+        <v>23</v>
+      </c>
+      <c r="AU3" s="8" t="s">
+        <v>2</v>
+      </c>
+      <c r="AV3" s="10" t="s">
+        <v>44</v>
+      </c>
+      <c r="AW3" s="9" t="s">
+        <v>2</v>
+      </c>
     </row>
-    <row r="4" spans="1:44" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:49" x14ac:dyDescent="0.25">
       <c r="A4" s="4" t="s">
         <v>4</v>
       </c>
@@ -1106,8 +1148,16 @@
         <v>13</v>
       </c>
       <c r="AR4" s="3"/>
+      <c r="AT4" s="4" t="s">
+        <v>4</v>
+      </c>
+      <c r="AU4" s="4"/>
+      <c r="AV4" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="AW4" s="3"/>
     </row>
-    <row r="5" spans="1:44" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:49" x14ac:dyDescent="0.25">
       <c r="A5" s="4" t="s">
         <v>5</v>
       </c>
@@ -1200,8 +1250,20 @@
         <v>14</v>
       </c>
       <c r="AR5" s="3"/>
+      <c r="AT5" s="4" t="s">
+        <v>31</v>
+      </c>
+      <c r="AU5" s="4">
+        <v>1</v>
+      </c>
+      <c r="AV5" s="3" t="s">
+        <v>14</v>
+      </c>
+      <c r="AW5" s="3">
+        <v>1</v>
+      </c>
     </row>
-    <row r="6" spans="1:44" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:49" x14ac:dyDescent="0.25">
       <c r="A6" s="4" t="s">
         <v>6</v>
       </c>
@@ -1294,8 +1356,18 @@
         <v>30</v>
       </c>
       <c r="AR6" s="3"/>
+      <c r="AT6" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="AU6" s="4">
+        <v>2</v>
+      </c>
+      <c r="AV6" s="3" t="s">
+        <v>30</v>
+      </c>
+      <c r="AW6" s="3"/>
     </row>
-    <row r="7" spans="1:44" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:49" x14ac:dyDescent="0.25">
       <c r="A7" s="4" t="s">
         <v>7</v>
       </c>
@@ -1388,8 +1460,20 @@
         <v>16</v>
       </c>
       <c r="AR7" s="3"/>
+      <c r="AT7" s="4" t="s">
+        <v>8</v>
+      </c>
+      <c r="AU7" s="4">
+        <v>1</v>
+      </c>
+      <c r="AV7" s="3" t="s">
+        <v>43</v>
+      </c>
+      <c r="AW7" s="3">
+        <v>1</v>
+      </c>
     </row>
-    <row r="8" spans="1:44" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:49" x14ac:dyDescent="0.25">
       <c r="A8" s="4" t="s">
         <v>8</v>
       </c>
@@ -1486,8 +1570,18 @@
         <v>5</v>
       </c>
       <c r="AR8" s="3"/>
+      <c r="AT8" s="4" t="s">
+        <v>35</v>
+      </c>
+      <c r="AU8" s="4">
+        <v>4</v>
+      </c>
+      <c r="AV8" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AW8" s="3"/>
     </row>
-    <row r="9" spans="1:44" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:49" x14ac:dyDescent="0.25">
       <c r="A9" s="4" t="s">
         <v>10</v>
       </c>
@@ -1586,8 +1680,20 @@
       <c r="AR9" s="3">
         <v>3</v>
       </c>
+      <c r="AT9" s="4" t="s">
+        <v>38</v>
+      </c>
+      <c r="AU9" s="4">
+        <v>3</v>
+      </c>
+      <c r="AV9" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="AW9" s="3">
+        <v>4</v>
+      </c>
     </row>
-    <row r="10" spans="1:44" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:49" x14ac:dyDescent="0.25">
       <c r="A10" s="4" t="s">
         <v>11</v>
       </c>
@@ -1690,8 +1796,20 @@
       <c r="AR10" s="3">
         <v>2</v>
       </c>
+      <c r="AT10" s="4" t="s">
+        <v>16</v>
+      </c>
+      <c r="AU10" s="4">
+        <v>2</v>
+      </c>
+      <c r="AV10" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="AW10" s="3">
+        <v>2</v>
+      </c>
     </row>
-    <row r="11" spans="1:44" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:49" x14ac:dyDescent="0.25">
       <c r="A11" s="4" t="s">
         <v>9</v>
       </c>
@@ -1750,8 +1868,14 @@
       <c r="AP11" s="4"/>
       <c r="AQ11" s="3"/>
       <c r="AR11" s="3"/>
+      <c r="AT11" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="AU11" s="4"/>
+      <c r="AV11" s="3"/>
+      <c r="AW11" s="3"/>
     </row>
-    <row r="12" spans="1:44" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:49" x14ac:dyDescent="0.25">
       <c r="A12" s="4"/>
       <c r="B12" s="4"/>
       <c r="C12" s="3"/>
@@ -1792,8 +1916,12 @@
       <c r="AP12" s="4"/>
       <c r="AQ12" s="3"/>
       <c r="AR12" s="3"/>
+      <c r="AT12" s="4"/>
+      <c r="AU12" s="4"/>
+      <c r="AV12" s="3"/>
+      <c r="AW12" s="3"/>
     </row>
-    <row r="13" spans="1:44" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:49" x14ac:dyDescent="0.25">
       <c r="A13" s="7" t="s">
         <v>19</v>
       </c>
@@ -1919,6 +2047,20 @@
       <c r="AR13" s="7">
         <f>SUM(AR2:AR12)</f>
         <v>5</v>
+      </c>
+      <c r="AT13" s="7" t="s">
+        <v>19</v>
+      </c>
+      <c r="AU13" s="7">
+        <f>SUM(AU2:AU12)</f>
+        <v>13</v>
+      </c>
+      <c r="AV13" s="7" t="s">
+        <v>22</v>
+      </c>
+      <c r="AW13" s="7">
+        <f>SUM(AW2:AW12)</f>
+        <v>8</v>
       </c>
     </row>
   </sheetData>

--- a/FCT.xlsx
+++ b/FCT.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/cc257be1a5798d86/WILLIAN/FCT Terça/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="285" documentId="13_ncr:1_{4721CD4C-DC5B-4D56-86E7-BD97B97F13DF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{EEA25F7C-C9B8-43A1-9E1B-5DC5FE06B562}"/>
+  <xr:revisionPtr revIDLastSave="320" documentId="13_ncr:1_{4721CD4C-DC5B-4D56-86E7-BD97B97F13DF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{6A318058-4C5A-4DDB-8D13-6D21D63588D7}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{4C5D2070-0CD2-4A2B-85DD-4C1228673220}"/>
   </bookViews>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="258" uniqueCount="45">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="283" uniqueCount="46">
   <si>
     <t>Azul</t>
   </si>
@@ -174,6 +174,9 @@
   </si>
   <si>
     <t>Goleiro sem nome</t>
+  </si>
+  <si>
+    <t>Edu Carlokoski</t>
   </si>
 </sst>
 </file>
@@ -705,7 +708,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8E481E65-1F7A-4C5C-8819-A9B2DFE6B944}">
-  <dimension ref="A1:AW13"/>
+  <dimension ref="A1:BB13"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="2" width="9.140625" style="1"/>
@@ -744,10 +747,14 @@
     <col min="46" max="46" width="11.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="47" max="47" width="9.140625" style="1"/>
     <col min="48" max="48" width="17.28515625" style="1" bestFit="1" customWidth="1"/>
-    <col min="49" max="16384" width="9.140625" style="1"/>
+    <col min="49" max="50" width="9.140625" style="1"/>
+    <col min="51" max="51" width="12.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="52" max="52" width="8.28515625" style="1" bestFit="1" customWidth="1"/>
+    <col min="53" max="53" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
+    <col min="54" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:49" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:54" x14ac:dyDescent="0.25">
       <c r="A1" s="2"/>
       <c r="B1" s="2" t="s">
         <v>20</v>
@@ -828,8 +835,16 @@
         <v>46308</v>
       </c>
       <c r="AW1" s="2"/>
+      <c r="AY1" s="2"/>
+      <c r="AZ1" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="BA1" s="2">
+        <v>46315</v>
+      </c>
+      <c r="BB1" s="2"/>
     </row>
-    <row r="2" spans="1:49" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:54" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A2" s="5" t="s">
         <v>0</v>
       </c>
@@ -950,8 +965,20 @@
       <c r="AW2" s="6" t="s">
         <v>18</v>
       </c>
+      <c r="AY2" s="5" t="s">
+        <v>0</v>
+      </c>
+      <c r="AZ2" s="5" t="s">
+        <v>18</v>
+      </c>
+      <c r="BA2" s="6" t="s">
+        <v>1</v>
+      </c>
+      <c r="BB2" s="6" t="s">
+        <v>18</v>
+      </c>
     </row>
-    <row r="3" spans="1:49" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:54" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A3" s="11" t="s">
         <v>3</v>
       </c>
@@ -1072,8 +1099,20 @@
       <c r="AW3" s="9" t="s">
         <v>2</v>
       </c>
+      <c r="AY3" s="11" t="s">
+        <v>26</v>
+      </c>
+      <c r="AZ3" s="8" t="s">
+        <v>2</v>
+      </c>
+      <c r="BA3" s="10" t="s">
+        <v>23</v>
+      </c>
+      <c r="BB3" s="9" t="s">
+        <v>2</v>
+      </c>
     </row>
-    <row r="4" spans="1:49" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:54" x14ac:dyDescent="0.25">
       <c r="A4" s="4" t="s">
         <v>4</v>
       </c>
@@ -1156,8 +1195,16 @@
         <v>13</v>
       </c>
       <c r="AW4" s="3"/>
+      <c r="AY4" s="4" t="s">
+        <v>30</v>
+      </c>
+      <c r="AZ4" s="4"/>
+      <c r="BA4" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="BB4" s="3"/>
     </row>
-    <row r="5" spans="1:49" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:54" x14ac:dyDescent="0.25">
       <c r="A5" s="4" t="s">
         <v>5</v>
       </c>
@@ -1262,8 +1309,18 @@
       <c r="AW5" s="3">
         <v>1</v>
       </c>
+      <c r="AY5" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="AZ5" s="4"/>
+      <c r="BA5" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="BB5" s="3">
+        <v>1</v>
+      </c>
     </row>
-    <row r="6" spans="1:49" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:54" x14ac:dyDescent="0.25">
       <c r="A6" s="4" t="s">
         <v>6</v>
       </c>
@@ -1366,8 +1423,16 @@
         <v>30</v>
       </c>
       <c r="AW6" s="3"/>
+      <c r="AY6" s="4" t="s">
+        <v>43</v>
+      </c>
+      <c r="AZ6" s="4"/>
+      <c r="BA6" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="BB6" s="3"/>
     </row>
-    <row r="7" spans="1:49" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:54" x14ac:dyDescent="0.25">
       <c r="A7" s="4" t="s">
         <v>7</v>
       </c>
@@ -1472,8 +1537,20 @@
       <c r="AW7" s="3">
         <v>1</v>
       </c>
+      <c r="AY7" s="4" t="s">
+        <v>5</v>
+      </c>
+      <c r="AZ7" s="4">
+        <v>1</v>
+      </c>
+      <c r="BA7" s="3" t="s">
+        <v>35</v>
+      </c>
+      <c r="BB7" s="3">
+        <v>1</v>
+      </c>
     </row>
-    <row r="8" spans="1:49" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:54" x14ac:dyDescent="0.25">
       <c r="A8" s="4" t="s">
         <v>8</v>
       </c>
@@ -1580,8 +1657,20 @@
         <v>5</v>
       </c>
       <c r="AW8" s="3"/>
+      <c r="AY8" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="AZ8" s="4">
+        <v>2</v>
+      </c>
+      <c r="BA8" s="3" t="s">
+        <v>45</v>
+      </c>
+      <c r="BB8" s="3">
+        <v>6</v>
+      </c>
     </row>
-    <row r="9" spans="1:49" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:54" x14ac:dyDescent="0.25">
       <c r="A9" s="4" t="s">
         <v>10</v>
       </c>
@@ -1692,8 +1781,20 @@
       <c r="AW9" s="3">
         <v>4</v>
       </c>
+      <c r="AY9" s="4" t="s">
+        <v>17</v>
+      </c>
+      <c r="AZ9" s="4">
+        <v>2</v>
+      </c>
+      <c r="BA9" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="BB9" s="3">
+        <v>6</v>
+      </c>
     </row>
-    <row r="10" spans="1:49" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:54" x14ac:dyDescent="0.25">
       <c r="A10" s="4" t="s">
         <v>11</v>
       </c>
@@ -1808,8 +1909,20 @@
       <c r="AW10" s="3">
         <v>2</v>
       </c>
+      <c r="AY10" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="AZ10" s="4">
+        <v>5</v>
+      </c>
+      <c r="BA10" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="BB10" s="3">
+        <v>1</v>
+      </c>
     </row>
-    <row r="11" spans="1:49" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:54" x14ac:dyDescent="0.25">
       <c r="A11" s="4" t="s">
         <v>9</v>
       </c>
@@ -1874,8 +1987,12 @@
       <c r="AU11" s="4"/>
       <c r="AV11" s="3"/>
       <c r="AW11" s="3"/>
+      <c r="AY11" s="4"/>
+      <c r="AZ11" s="4"/>
+      <c r="BA11" s="3"/>
+      <c r="BB11" s="3"/>
     </row>
-    <row r="12" spans="1:49" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:54" x14ac:dyDescent="0.25">
       <c r="A12" s="4"/>
       <c r="B12" s="4"/>
       <c r="C12" s="3"/>
@@ -1920,8 +2037,12 @@
       <c r="AU12" s="4"/>
       <c r="AV12" s="3"/>
       <c r="AW12" s="3"/>
+      <c r="AY12" s="4"/>
+      <c r="AZ12" s="4"/>
+      <c r="BA12" s="3"/>
+      <c r="BB12" s="3"/>
     </row>
-    <row r="13" spans="1:49" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:54" x14ac:dyDescent="0.25">
       <c r="A13" s="7" t="s">
         <v>19</v>
       </c>
@@ -2061,6 +2182,20 @@
       <c r="AW13" s="7">
         <f>SUM(AW2:AW12)</f>
         <v>8</v>
+      </c>
+      <c r="AY13" s="7" t="s">
+        <v>19</v>
+      </c>
+      <c r="AZ13" s="7">
+        <f>SUM(AZ2:AZ12)</f>
+        <v>10</v>
+      </c>
+      <c r="BA13" s="7" t="s">
+        <v>22</v>
+      </c>
+      <c r="BB13" s="7">
+        <f>SUM(BB2:BB12)</f>
+        <v>15</v>
       </c>
     </row>
   </sheetData>

--- a/FCT.xlsx
+++ b/FCT.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30430"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30527"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/cc257be1a5798d86/WILLIAN/FCT Terça/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="320" documentId="13_ncr:1_{4721CD4C-DC5B-4D56-86E7-BD97B97F13DF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{6A318058-4C5A-4DDB-8D13-6D21D63588D7}"/>
+  <xr:revisionPtr revIDLastSave="347" documentId="13_ncr:1_{4721CD4C-DC5B-4D56-86E7-BD97B97F13DF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{05B18A06-A7B8-4466-B529-861C01214A4D}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{4C5D2070-0CD2-4A2B-85DD-4C1228673220}"/>
   </bookViews>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="283" uniqueCount="46">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="309" uniqueCount="46">
   <si>
     <t>Azul</t>
   </si>
@@ -708,7 +708,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8E481E65-1F7A-4C5C-8819-A9B2DFE6B944}">
-  <dimension ref="A1:BB13"/>
+  <dimension ref="A1:BG13"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="2" width="9.140625" style="1"/>
@@ -751,10 +751,14 @@
     <col min="51" max="51" width="12.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="52" max="52" width="8.28515625" style="1" bestFit="1" customWidth="1"/>
     <col min="53" max="53" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
-    <col min="54" max="16384" width="9.140625" style="1"/>
+    <col min="54" max="55" width="9.140625" style="1"/>
+    <col min="56" max="56" width="17.28515625" style="1" bestFit="1" customWidth="1"/>
+    <col min="57" max="57" width="9.140625" style="1"/>
+    <col min="58" max="58" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
+    <col min="59" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:54" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:59" x14ac:dyDescent="0.25">
       <c r="A1" s="2"/>
       <c r="B1" s="2" t="s">
         <v>20</v>
@@ -843,8 +847,16 @@
         <v>46315</v>
       </c>
       <c r="BB1" s="2"/>
+      <c r="BD1" s="2"/>
+      <c r="BE1" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="BF1" s="2">
+        <v>46322</v>
+      </c>
+      <c r="BG1" s="2"/>
     </row>
-    <row r="2" spans="1:54" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:59" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A2" s="5" t="s">
         <v>0</v>
       </c>
@@ -977,8 +989,20 @@
       <c r="BB2" s="6" t="s">
         <v>18</v>
       </c>
+      <c r="BD2" s="5" t="s">
+        <v>0</v>
+      </c>
+      <c r="BE2" s="5" t="s">
+        <v>18</v>
+      </c>
+      <c r="BF2" s="6" t="s">
+        <v>1</v>
+      </c>
+      <c r="BG2" s="6" t="s">
+        <v>18</v>
+      </c>
     </row>
-    <row r="3" spans="1:54" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:59" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A3" s="11" t="s">
         <v>3</v>
       </c>
@@ -1111,8 +1135,20 @@
       <c r="BB3" s="9" t="s">
         <v>2</v>
       </c>
+      <c r="BD3" s="11" t="s">
+        <v>44</v>
+      </c>
+      <c r="BE3" s="8" t="s">
+        <v>2</v>
+      </c>
+      <c r="BF3" s="10" t="s">
+        <v>23</v>
+      </c>
+      <c r="BG3" s="9" t="s">
+        <v>2</v>
+      </c>
     </row>
-    <row r="4" spans="1:54" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:59" x14ac:dyDescent="0.25">
       <c r="A4" s="4" t="s">
         <v>4</v>
       </c>
@@ -1203,8 +1239,16 @@
         <v>12</v>
       </c>
       <c r="BB4" s="3"/>
+      <c r="BD4" s="4" t="s">
+        <v>30</v>
+      </c>
+      <c r="BE4" s="4"/>
+      <c r="BF4" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="BG4" s="3"/>
     </row>
-    <row r="5" spans="1:54" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:59" x14ac:dyDescent="0.25">
       <c r="A5" s="4" t="s">
         <v>5</v>
       </c>
@@ -1319,8 +1363,16 @@
       <c r="BB5" s="3">
         <v>1</v>
       </c>
+      <c r="BD5" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="BE5" s="4"/>
+      <c r="BF5" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="BG5" s="3"/>
     </row>
-    <row r="6" spans="1:54" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:59" x14ac:dyDescent="0.25">
       <c r="A6" s="4" t="s">
         <v>6</v>
       </c>
@@ -1431,8 +1483,18 @@
         <v>8</v>
       </c>
       <c r="BB6" s="3"/>
+      <c r="BD6" s="4" t="s">
+        <v>4</v>
+      </c>
+      <c r="BE6" s="4"/>
+      <c r="BF6" s="3" t="s">
+        <v>14</v>
+      </c>
+      <c r="BG6" s="3">
+        <v>1</v>
+      </c>
     </row>
-    <row r="7" spans="1:54" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:59" x14ac:dyDescent="0.25">
       <c r="A7" s="4" t="s">
         <v>7</v>
       </c>
@@ -1549,8 +1611,20 @@
       <c r="BB7" s="3">
         <v>1</v>
       </c>
+      <c r="BD7" s="4" t="s">
+        <v>5</v>
+      </c>
+      <c r="BE7" s="4">
+        <v>3</v>
+      </c>
+      <c r="BF7" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="BG7" s="3">
+        <v>1</v>
+      </c>
     </row>
-    <row r="8" spans="1:54" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:59" x14ac:dyDescent="0.25">
       <c r="A8" s="4" t="s">
         <v>8</v>
       </c>
@@ -1669,8 +1743,20 @@
       <c r="BB8" s="3">
         <v>6</v>
       </c>
+      <c r="BD8" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="BE8" s="4">
+        <v>2</v>
+      </c>
+      <c r="BF8" s="3" t="s">
+        <v>38</v>
+      </c>
+      <c r="BG8" s="3">
+        <v>4</v>
+      </c>
     </row>
-    <row r="9" spans="1:54" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:59" x14ac:dyDescent="0.25">
       <c r="A9" s="4" t="s">
         <v>10</v>
       </c>
@@ -1793,8 +1879,20 @@
       <c r="BB9" s="3">
         <v>6</v>
       </c>
+      <c r="BD9" s="4" t="s">
+        <v>45</v>
+      </c>
+      <c r="BE9" s="4">
+        <v>5</v>
+      </c>
+      <c r="BF9" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="BG9" s="3">
+        <v>2</v>
+      </c>
     </row>
-    <row r="10" spans="1:54" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:59" x14ac:dyDescent="0.25">
       <c r="A10" s="4" t="s">
         <v>11</v>
       </c>
@@ -1921,8 +2019,20 @@
       <c r="BB10" s="3">
         <v>1</v>
       </c>
+      <c r="BD10" s="4" t="s">
+        <v>14</v>
+      </c>
+      <c r="BE10" s="4">
+        <v>4</v>
+      </c>
+      <c r="BF10" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="BG10" s="3">
+        <v>4</v>
+      </c>
     </row>
-    <row r="11" spans="1:54" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:59" x14ac:dyDescent="0.25">
       <c r="A11" s="4" t="s">
         <v>9</v>
       </c>
@@ -1991,8 +2101,14 @@
       <c r="AZ11" s="4"/>
       <c r="BA11" s="3"/>
       <c r="BB11" s="3"/>
+      <c r="BD11" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="BE11" s="4"/>
+      <c r="BF11" s="3"/>
+      <c r="BG11" s="3"/>
     </row>
-    <row r="12" spans="1:54" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:59" x14ac:dyDescent="0.25">
       <c r="A12" s="4"/>
       <c r="B12" s="4"/>
       <c r="C12" s="3"/>
@@ -2041,8 +2157,12 @@
       <c r="AZ12" s="4"/>
       <c r="BA12" s="3"/>
       <c r="BB12" s="3"/>
+      <c r="BD12" s="4"/>
+      <c r="BE12" s="4"/>
+      <c r="BF12" s="3"/>
+      <c r="BG12" s="3"/>
     </row>
-    <row r="13" spans="1:54" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:59" x14ac:dyDescent="0.25">
       <c r="A13" s="7" t="s">
         <v>19</v>
       </c>
@@ -2196,6 +2316,20 @@
       <c r="BB13" s="7">
         <f>SUM(BB2:BB12)</f>
         <v>15</v>
+      </c>
+      <c r="BD13" s="7" t="s">
+        <v>19</v>
+      </c>
+      <c r="BE13" s="7">
+        <f>SUM(BE2:BE12)</f>
+        <v>14</v>
+      </c>
+      <c r="BF13" s="7" t="s">
+        <v>22</v>
+      </c>
+      <c r="BG13" s="7">
+        <f>SUM(BG2:BG12)</f>
+        <v>12</v>
       </c>
     </row>
   </sheetData>
